--- a/artfynd/A 68700-2021 artfynd.xlsx
+++ b/artfynd/A 68700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122756846</v>
       </c>
       <c r="B2" t="n">
-        <v>95118</v>
+        <v>95126</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 68700-2021 artfynd.xlsx
+++ b/artfynd/A 68700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122756846</v>
       </c>
       <c r="B2" t="n">
-        <v>95126</v>
+        <v>95128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 68700-2021 artfynd.xlsx
+++ b/artfynd/A 68700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122756846</v>
       </c>
       <c r="B2" t="n">
-        <v>95128</v>
+        <v>95136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 68700-2021 artfynd.xlsx
+++ b/artfynd/A 68700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122756846</v>
       </c>
       <c r="B2" t="n">
-        <v>95136</v>
+        <v>95139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 68700-2021 artfynd.xlsx
+++ b/artfynd/A 68700-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122756846</v>
       </c>
       <c r="B2" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 68700-2021 artfynd.xlsx
+++ b/artfynd/A 68700-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>122756846</v>
       </c>
       <c r="B2" t="n">
-        <v>95141</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,6 +779,219 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127737521</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Övre Söderby, Övre Söderby, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>658302</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6566873</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>89993702</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Övre Söderby, Salem, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>658439</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6566849</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-01-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-01-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Almqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Almqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 68700-2021 artfynd.xlsx
+++ b/artfynd/A 68700-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122756846</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127737521</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,8 +1007,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89993702</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>